--- a/samples/inventaire_exemple.xlsx
+++ b/samples/inventaire_exemple.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Stock theorique" sheetId="1" r:id="rId1"/>
+    <sheet name="in" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -44,57 +44,67 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>code_article</t>
+          <t>PID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>code_barre</t>
+          <t>Produit</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>reference</t>
+          <t>Catégorie</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>designation</t>
+          <t>TVA</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>PPV</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>categorie</t>
+          <t>PPH</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>emplacement</t>
+          <t>Zone</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>quantite_theorique</t>
+          <t>Stock</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>unite</t>
+          <t>Date de péremption</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>prix_unitaire</t>
+          <t>Stock min</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>date_import</t>
+          <t>Stock max</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Code barre 1</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Code barre 2</t>
         </is>
       </c>
     </row>
@@ -106,52 +116,62 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Enveloppes A4 blanches</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fournitures bureau</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TVA (20.00%)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>45.50</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>37.90</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Dépôt A - Rayon 3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>6111234500018</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>REF-ENV-A4</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Enveloppes A4 blanches</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Boîte de 500 enveloppes A4 90g</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Fournitures bureau</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Dépôt A - Rayon 3</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>boite</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>45.50</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
@@ -163,52 +183,62 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Timbres ordinaires</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Philatélie</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Exonéré (0.00%)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dépôt A - Rayon 1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>6111234500025</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>REF-TIMB-ORD</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Timbres ordinaires</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Carnet de 10 timbres tarif prioritaire</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Philatélie</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Dépôt A - Rayon 1</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>carnet</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
@@ -220,52 +250,62 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Timbres ordinaires</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Philatélie</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Exonéré (0.00%)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dépôt A - Rayon 1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>6111234500032</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>REF-TIMB-ORD</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Timbres ordinaires</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Carnet de 10 timbres tarif prioritaire</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Philatélie</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Dépôt A - Rayon 1</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>carnet</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>12.00</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
@@ -277,27 +317,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6111234500049,6111234500056</t>
+          <t>Cartons colis M</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>REF-CART-COL</t>
+          <t>Emballage</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cartons colis M</t>
+          <t>TVA (20.00%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Carton d'expédition format M</t>
+          <t>8.75</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Emballage</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -312,17 +352,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>unite</t>
+          <t/>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6111234500049</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6111234500056</t>
         </is>
       </c>
     </row>
@@ -334,52 +384,62 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Rouleau adhésif</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Emballage</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TVA (20.00%)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dépôt B - Rayon 2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>6111234500063</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>REF-SCOT</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Rouleau adhésif</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Scotch d'emballage 48mm</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Emballage</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Dépôt B - Rayon 2</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>unite</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
@@ -435,6 +495,16 @@
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t/>
         </is>
